--- a/PJT1_IOclass.xlsx
+++ b/PJT1_IOclass.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAN-Notebook\Desktop\PJT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F9BABA-C072-4EE8-A747-193CB5D68729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D96954D-6A94-48AF-A624-BD8CBA5B92EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Class IoPoint" sheetId="3" r:id="rId1"/>
+    <sheet name="Class IOPoint" sheetId="3" r:id="rId1"/>
     <sheet name="Id (Identification) class" sheetId="4" r:id="rId2"/>
     <sheet name="Industrial Tag Parser" sheetId="5" r:id="rId3"/>
   </sheets>
